--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -2795,11 +2795,11 @@
         <v>5732</v>
       </c>
       <c r="H14" s="29">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>19717</v>
+        <v>19617</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -2779,12 +2779,8 @@
       <c r="B14" s="29">
         <v>336</v>
       </c>
-      <c r="C14" s="29">
-        <v>3</v>
-      </c>
-      <c r="D14" s="29">
-        <v>5</v>
-      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="29">
         <v>13440</v>
       </c>
@@ -2795,11 +2791,11 @@
         <v>5732</v>
       </c>
       <c r="H14" s="29">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>19617</v>
+        <v>19709</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -2784,9 +2784,7 @@
       <c r="E14" s="29">
         <v>13440</v>
       </c>
-      <c r="F14" s="29">
-        <v>1</v>
-      </c>
+      <c r="F14" s="29"/>
       <c r="G14" s="29">
         <v>5732</v>
       </c>
@@ -2795,7 +2793,7 @@
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>19709</v>
+        <v>19708</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
     <sheet name="01_재해설정" sheetId="2" r:id="rId2"/>
     <sheet name="폭염" sheetId="3" r:id="rId3"/>
-    <sheet name="호우" sheetId="4" r:id="rId4"/>
+    <sheet name="호우" sheetId="11" r:id="rId4"/>
     <sheet name="태풍" sheetId="5" r:id="rId5"/>
     <sheet name="산불" sheetId="6" r:id="rId6"/>
     <sheet name="대설" sheetId="7" r:id="rId7"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="152">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -515,6 +515,35 @@
     <t>구호품목 표준화 검토</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>구호키트</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>세탁차량</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>소방관</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출동키트</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원봉사자키트</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -525,7 +554,7 @@
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -611,6 +640,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="돋움"/>
       <family val="3"/>
@@ -897,7 +934,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1126,6 +1163,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1960,12 +2000,24 @@
       <c r="A15" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
+      <c r="B15" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>100</v>
+      </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
@@ -2747,26 +2799,26 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>63</v>
+      <c r="B13" s="81" t="s">
+        <v>148</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>69</v>
+      <c r="F13" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>149</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>70</v>
@@ -2779,18 +2831,18 @@
       <c r="B14" s="29">
         <v>336</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="C14" s="29">
+        <v>200</v>
+      </c>
+      <c r="D14" s="29">
+        <v>13440</v>
+      </c>
       <c r="E14" s="29">
-        <v>13440</v>
+        <v>5732</v>
       </c>
       <c r="F14" s="29"/>
-      <c r="G14" s="29">
-        <v>5732</v>
-      </c>
-      <c r="H14" s="29">
-        <v>200</v>
-      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
         <v>19708</v>
@@ -2804,23 +2856,21 @@
         <v>97</v>
       </c>
       <c r="C15" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="32" t="s">
         <v>97</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>99</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>98</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9">
@@ -3419,26 +3469,26 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>63</v>
+      <c r="B13" s="81" t="s">
+        <v>148</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>69</v>
+      <c r="F13" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>149</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>70</v>
@@ -3475,18 +3525,22 @@
       <c r="B15" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="E15" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="32"/>
+        <v>97</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>100</v>
+      </c>
       <c r="G15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>98</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:10">
@@ -4115,26 +4169,26 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>63</v>
+      <c r="B13" s="81" t="s">
+        <v>148</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>69</v>
+      <c r="F13" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>149</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>70</v>
@@ -4171,18 +4225,22 @@
       <c r="B15" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="E15" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="32"/>
+        <v>97</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>100</v>
+      </c>
       <c r="G15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>98</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:10">
@@ -4811,26 +4869,26 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>63</v>
+      <c r="B13" s="81" t="s">
+        <v>148</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>69</v>
+      <c r="F13" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>149</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>70</v>
@@ -4867,18 +4925,22 @@
       <c r="B15" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="E15" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="32"/>
+        <v>97</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>100</v>
+      </c>
       <c r="G15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>98</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:10">
@@ -5507,26 +5569,26 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>63</v>
+      <c r="B13" s="81" t="s">
+        <v>148</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>69</v>
+      <c r="F13" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>149</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>70</v>
@@ -5563,18 +5625,22 @@
       <c r="B15" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="E15" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="32"/>
+        <v>97</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>100</v>
+      </c>
       <c r="G15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>98</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:10">

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="148">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -217,19 +217,7 @@
     <t>지표단위</t>
   </si>
   <si>
-    <t>일시구호세트</t>
-  </si>
-  <si>
-    <t>취사세트</t>
-  </si>
-  <si>
-    <t>희망하우스</t>
-  </si>
-  <si>
     <t>생수</t>
-  </si>
-  <si>
-    <t>소방관지원세트</t>
   </si>
   <si>
     <t>간식</t>
@@ -1119,6 +1107,9 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1163,9 +1154,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1389,28 +1377,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="67" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1422,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
@@ -1433,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.5">
@@ -1452,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
@@ -1500,31 +1488,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="67" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1754,31 +1742,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="68" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1923,31 +1911,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
+      <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1955,45 +1943,55 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="66" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="E13" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="26" t="s">
+      <c r="F13" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
+      <c r="C14" s="29">
+        <v>200</v>
+      </c>
       <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
+      <c r="E14" s="29">
+        <v>5732</v>
+      </c>
+      <c r="F14" s="29">
+        <v>500</v>
+      </c>
+      <c r="G14" s="29">
+        <v>500</v>
+      </c>
+      <c r="H14" s="29">
+        <v>5</v>
+      </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>0</v>
+        <v>6937</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2001,22 +1999,22 @@
         <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -2033,31 +2031,31 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J17" s="35"/>
@@ -2065,19 +2063,19 @@
     </row>
     <row r="18" spans="1:11" ht="15">
       <c r="A18" s="25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>28</v>
@@ -2089,18 +2087,18 @@
         <v>31</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="36" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B19" s="37"/>
       <c r="C19" s="37"/>
@@ -2121,7 +2119,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="41" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -2146,7 +2144,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -2169,7 +2167,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -2190,7 +2188,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="41" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -2213,7 +2211,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="41" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
@@ -2234,7 +2232,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="41" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
@@ -2255,7 +2253,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="41" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -2276,7 +2274,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="41" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -2299,7 +2297,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -2324,7 +2322,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -2347,7 +2345,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -2372,7 +2370,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="41" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -2397,7 +2395,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
@@ -2422,7 +2420,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
@@ -2449,7 +2447,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="46" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="47"/>
@@ -2489,7 +2487,7 @@
     </row>
     <row r="36" spans="1:11" ht="15">
       <c r="A36" s="25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -2532,32 +2530,32 @@
       <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="69"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
+      <c r="A38" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="69"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="70"/>
-      <c r="K39" s="70"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="17"/>
@@ -2596,32 +2594,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>96</v>
+      <c r="A1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2767,31 +2765,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
+      <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2799,34 +2797,34 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>148</v>
+      <c r="B13" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29">
         <v>336</v>
@@ -2853,22 +2851,22 @@
         <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -2885,31 +2883,31 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2921,16 +2919,16 @@
         <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>30</v>
@@ -2944,10 +2942,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="36" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -2965,10 +2963,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -2984,11 +2982,11 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -2998,16 +2996,16 @@
       <c r="G21" s="43"/>
       <c r="H21" s="43"/>
       <c r="I21" s="55" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -3017,15 +3015,15 @@
       <c r="G22" s="43"/>
       <c r="H22" s="43"/>
       <c r="I22" s="55" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
@@ -3039,10 +3037,10 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C24" s="42"/>
       <c r="D24" s="42"/>
@@ -3056,7 +3054,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="46" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
@@ -3068,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="57" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3261,35 +3259,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="66" t="s">
-        <v>110</v>
+      <c r="A1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3311,14 +3309,14 @@
         <v>39</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -3328,12 +3326,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="76"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -3343,12 +3341,12 @@
         <v>46269</v>
       </c>
       <c r="C5" s="17"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -3437,31 +3435,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
+      <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3469,40 +3467,42 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>148</v>
+      <c r="B13" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29">
         <v>120</v>
       </c>
       <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="D14" s="29">
+        <v>50000</v>
+      </c>
       <c r="E14" s="29">
         <v>4800</v>
       </c>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>6460</v>
+        <v>56460</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3523,22 +3523,22 @@
         <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -3555,34 +3555,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="80" t="s">
+      <c r="J17" s="81" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3594,36 +3594,36 @@
         <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H18" s="26" t="s">
         <v>44</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="41" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="46" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
@@ -3961,35 +3961,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="J1" s="66" t="s">
-        <v>121</v>
+      <c r="A1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4011,14 +4011,14 @@
         <v>46</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -4028,12 +4028,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="76"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -4043,12 +4043,12 @@
         <v>46099</v>
       </c>
       <c r="C5" s="17"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -4137,31 +4137,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
+      <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4169,34 +4169,34 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>148</v>
+      <c r="B13" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29">
         <v>210</v>
@@ -4207,15 +4207,13 @@
         <v>7200</v>
       </c>
       <c r="F14" s="29"/>
-      <c r="G14" s="29">
-        <v>3200</v>
-      </c>
+      <c r="G14" s="29"/>
       <c r="H14" s="29">
         <v>65</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>10675</v>
+        <v>7475</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4223,22 +4221,22 @@
         <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -4255,34 +4253,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="80" t="s">
+      <c r="J17" s="81" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4294,22 +4292,22 @@
         <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>44</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>30</v>
@@ -4320,10 +4318,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="36" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -4346,10 +4344,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -4372,10 +4370,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -4398,10 +4396,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -4424,10 +4422,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="46" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
@@ -4661,35 +4659,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="F1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="J1" s="66" t="s">
-        <v>128</v>
+      <c r="A1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4711,14 +4709,14 @@
         <v>50</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -4728,12 +4726,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="76"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -4743,12 +4741,12 @@
         <v>46038</v>
       </c>
       <c r="C5" s="17"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -4837,31 +4835,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
+      <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4869,53 +4867,53 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>148</v>
+      <c r="B13" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29">
-        <v>80</v>
-      </c>
-      <c r="C14" s="29"/>
+        <v>3050</v>
+      </c>
+      <c r="C14" s="29">
+        <v>750</v>
+      </c>
       <c r="D14" s="29"/>
       <c r="E14" s="29">
         <v>2100</v>
       </c>
       <c r="F14" s="29"/>
-      <c r="G14" s="29">
-        <v>980</v>
-      </c>
+      <c r="G14" s="29"/>
       <c r="H14" s="29">
         <v>30</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>3190</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4923,22 +4921,22 @@
         <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -4955,34 +4953,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="80" t="s">
+      <c r="J17" s="81" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4994,36 +4992,36 @@
         <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H18" s="26" t="s">
         <v>54</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="36" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -5046,10 +5044,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -5072,10 +5070,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -5098,10 +5096,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -5124,10 +5122,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="46" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
@@ -5361,35 +5359,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="G1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="J1" s="66" t="s">
-        <v>137</v>
+      <c r="A1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5411,14 +5409,14 @@
         <v>55</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -5428,12 +5426,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="76"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -5443,12 +5441,12 @@
         <v>46153</v>
       </c>
       <c r="C5" s="17"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -5537,31 +5535,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
+      <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5569,34 +5567,34 @@
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>148</v>
+      <c r="B13" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29">
         <v>55</v>
@@ -5606,16 +5604,16 @@
       <c r="E14" s="29">
         <v>1600</v>
       </c>
-      <c r="F14" s="29"/>
+      <c r="F14" s="29">
+        <v>20</v>
+      </c>
       <c r="G14" s="29">
-        <v>620</v>
-      </c>
-      <c r="H14" s="29">
         <v>20</v>
       </c>
+      <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>2295</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5623,22 +5621,22 @@
         <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -5655,34 +5653,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="80" t="s">
+      <c r="J17" s="81" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5694,36 +5692,36 @@
         <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>44</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="36" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -5746,10 +5744,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -5772,10 +5770,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -5798,10 +5796,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -5824,10 +5822,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="46" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="127">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -362,45 +362,12 @@
     <t>정전가구</t>
   </si>
   <si>
-    <t>기장군</t>
-  </si>
-  <si>
-    <t>거제시</t>
-  </si>
-  <si>
-    <t>전남</t>
-  </si>
-  <si>
-    <t>여수시</t>
-  </si>
-  <si>
-    <t>서귀포시</t>
-  </si>
-  <si>
-    <t>울주군</t>
-  </si>
-  <si>
     <t>재난 및 구호 현장지도 데이터 - 산불</t>
   </si>
   <si>
     <t>산불피해면적(ha)</t>
   </si>
   <si>
-    <t>의성군</t>
-  </si>
-  <si>
-    <t>산청군</t>
-  </si>
-  <si>
-    <t>삼척시</t>
-  </si>
-  <si>
-    <t>영동군</t>
-  </si>
-  <si>
-    <t>순천시</t>
-  </si>
-  <si>
     <t>재난 및 구호 현장지도 데이터 - 대설</t>
   </si>
   <si>
@@ -413,21 +380,6 @@
     <t>교통통제(개소)</t>
   </si>
   <si>
-    <t>평창군</t>
-  </si>
-  <si>
-    <t>무주군</t>
-  </si>
-  <si>
-    <t>제천시</t>
-  </si>
-  <si>
-    <t>봉화군</t>
-  </si>
-  <si>
-    <t>포천시</t>
-  </si>
-  <si>
     <t>재난 및 구호 현장지도 데이터 - 지진</t>
   </si>
   <si>
@@ -435,21 +387,6 @@
   </si>
   <si>
     <t>여진횟수</t>
-  </si>
-  <si>
-    <t>경주시</t>
-  </si>
-  <si>
-    <t>북구</t>
-  </si>
-  <si>
-    <t>금정구</t>
-  </si>
-  <si>
-    <t>양산시</t>
-  </si>
-  <si>
-    <t>동구</t>
   </si>
   <si>
     <t>검토사항</t>
@@ -1410,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
@@ -1421,7 +1358,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.5">
@@ -1440,7 +1377,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
@@ -1730,6 +1667,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1944,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>65</v>
@@ -1956,13 +1896,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>66</v>
@@ -1973,25 +1913,15 @@
         <v>67</v>
       </c>
       <c r="B14" s="29"/>
-      <c r="C14" s="29">
-        <v>200</v>
-      </c>
+      <c r="C14" s="29"/>
       <c r="D14" s="29"/>
-      <c r="E14" s="29">
-        <v>5732</v>
-      </c>
-      <c r="F14" s="29">
-        <v>500</v>
-      </c>
-      <c r="G14" s="29">
-        <v>500</v>
-      </c>
-      <c r="H14" s="29">
-        <v>5</v>
-      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>6937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2577,6 +2507,7 @@
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2798,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>65</v>
@@ -2810,13 +2741,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>66</v>
@@ -3468,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>65</v>
@@ -3480,13 +3411,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>66</v>
@@ -3496,27 +3427,14 @@
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="29">
-        <v>120</v>
-      </c>
+      <c r="B14" s="29"/>
       <c r="C14" s="29"/>
-      <c r="D14" s="29">
-        <v>50000</v>
-      </c>
-      <c r="E14" s="29">
-        <v>4800</v>
-      </c>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="29"/>
-      <c r="G14" s="29">
-        <v>1500</v>
-      </c>
-      <c r="H14" s="29">
-        <v>40</v>
-      </c>
-      <c r="I14" s="30">
-        <f>SUM(B14:H14)</f>
-        <v>56460</v>
-      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
@@ -3619,134 +3537,64 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>111</v>
-      </c>
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
       <c r="E19" s="37"/>
-      <c r="F19" s="58">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="G19" s="58">
-        <v>312.39999999999998</v>
-      </c>
-      <c r="H19" s="58">
-        <v>84</v>
-      </c>
-      <c r="I19" s="58">
-        <v>12</v>
-      </c>
-      <c r="J19" s="59">
-        <v>130</v>
-      </c>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>112</v>
-      </c>
+      <c r="A20" s="41"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
-      <c r="F20" s="60">
-        <v>42.1</v>
-      </c>
-      <c r="G20" s="60">
-        <v>356.8</v>
-      </c>
-      <c r="H20" s="60">
-        <v>126</v>
-      </c>
-      <c r="I20" s="60">
-        <v>18</v>
-      </c>
-      <c r="J20" s="61">
-        <v>240</v>
-      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>114</v>
-      </c>
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
-      <c r="F21" s="60">
-        <v>35.4</v>
-      </c>
-      <c r="G21" s="60">
-        <v>271.2</v>
-      </c>
-      <c r="H21" s="60">
-        <v>63</v>
-      </c>
-      <c r="I21" s="60">
-        <v>7</v>
-      </c>
-      <c r="J21" s="61">
-        <v>85</v>
-      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>115</v>
-      </c>
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
-      <c r="F22" s="60">
-        <v>46.8</v>
-      </c>
-      <c r="G22" s="60">
-        <v>410.5</v>
-      </c>
-      <c r="H22" s="60">
-        <v>205</v>
-      </c>
-      <c r="I22" s="60">
-        <v>24</v>
-      </c>
-      <c r="J22" s="61">
-        <v>310</v>
-      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="61"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>116</v>
-      </c>
+      <c r="A23" s="46"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="F23" s="62">
-        <v>33.9</v>
-      </c>
-      <c r="G23" s="62">
-        <v>198.7</v>
-      </c>
-      <c r="H23" s="62">
-        <v>41</v>
-      </c>
-      <c r="I23" s="62">
-        <v>5</v>
-      </c>
-      <c r="J23" s="63">
-        <v>70</v>
-      </c>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="17"/>
@@ -3962,34 +3810,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I1" s="68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J1" s="67" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4170,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>65</v>
@@ -4182,13 +4030,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>66</v>
@@ -4198,23 +4046,14 @@
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="29">
-        <v>210</v>
-      </c>
+      <c r="B14" s="29"/>
       <c r="C14" s="29"/>
       <c r="D14" s="29"/>
-      <c r="E14" s="29">
-        <v>7200</v>
-      </c>
+      <c r="E14" s="29"/>
       <c r="F14" s="29"/>
       <c r="G14" s="29"/>
-      <c r="H14" s="29">
-        <v>65</v>
-      </c>
-      <c r="I14" s="30">
-        <f>SUM(B14:H14)</f>
-        <v>7475</v>
-      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
@@ -4301,7 +4140,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>44</v>
@@ -4317,134 +4156,64 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>119</v>
-      </c>
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
       <c r="E19" s="37"/>
-      <c r="F19" s="58">
-        <v>1840</v>
-      </c>
-      <c r="G19" s="58">
-        <v>740</v>
-      </c>
-      <c r="H19" s="58">
-        <v>31</v>
-      </c>
-      <c r="I19" s="58">
-        <v>0</v>
-      </c>
-      <c r="J19" s="59">
-        <v>4</v>
-      </c>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>120</v>
-      </c>
+      <c r="A20" s="41"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
-      <c r="F20" s="60">
-        <v>920</v>
-      </c>
-      <c r="G20" s="60">
-        <v>365</v>
-      </c>
-      <c r="H20" s="60">
-        <v>14</v>
-      </c>
-      <c r="I20" s="60">
-        <v>0</v>
-      </c>
-      <c r="J20" s="61">
-        <v>2</v>
-      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>121</v>
-      </c>
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
-      <c r="F21" s="60">
-        <v>610</v>
-      </c>
-      <c r="G21" s="60">
-        <v>205</v>
-      </c>
-      <c r="H21" s="60">
-        <v>8</v>
-      </c>
-      <c r="I21" s="60">
-        <v>0</v>
-      </c>
-      <c r="J21" s="61">
-        <v>1</v>
-      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>122</v>
-      </c>
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
-      <c r="F22" s="60">
-        <v>275</v>
-      </c>
-      <c r="G22" s="60">
-        <v>92</v>
-      </c>
-      <c r="H22" s="60">
-        <v>3</v>
-      </c>
-      <c r="I22" s="60">
-        <v>0</v>
-      </c>
-      <c r="J22" s="61">
-        <v>0</v>
-      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="61"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>123</v>
-      </c>
+      <c r="A23" s="46"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="F23" s="62">
-        <v>160</v>
-      </c>
-      <c r="G23" s="62">
-        <v>51</v>
-      </c>
-      <c r="H23" s="62">
-        <v>1</v>
-      </c>
-      <c r="I23" s="62">
-        <v>0</v>
-      </c>
-      <c r="J23" s="63">
-        <v>0</v>
-      </c>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="17"/>
@@ -4660,34 +4429,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I1" s="68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J1" s="67" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4868,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>65</v>
@@ -4880,13 +4649,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>66</v>
@@ -4896,25 +4665,14 @@
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="29">
-        <v>3050</v>
-      </c>
-      <c r="C14" s="29">
-        <v>750</v>
-      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
       <c r="D14" s="29"/>
-      <c r="E14" s="29">
-        <v>2100</v>
-      </c>
+      <c r="E14" s="29"/>
       <c r="F14" s="29"/>
       <c r="G14" s="29"/>
-      <c r="H14" s="29">
-        <v>30</v>
-      </c>
-      <c r="I14" s="30">
-        <f>SUM(B14:H14)</f>
-        <v>5930</v>
-      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
@@ -5001,150 +4759,80 @@
         <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H18" s="26" t="s">
         <v>54</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>128</v>
-      </c>
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
       <c r="E19" s="37"/>
-      <c r="F19" s="58">
-        <v>48.3</v>
-      </c>
-      <c r="G19" s="58">
-        <v>27</v>
-      </c>
-      <c r="H19" s="58">
-        <v>34</v>
-      </c>
-      <c r="I19" s="58">
-        <v>9</v>
-      </c>
-      <c r="J19" s="59">
-        <v>80</v>
-      </c>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>129</v>
-      </c>
+      <c r="A20" s="41"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
-      <c r="F20" s="60">
-        <v>41.5</v>
-      </c>
-      <c r="G20" s="60">
-        <v>18</v>
-      </c>
-      <c r="H20" s="60">
-        <v>22</v>
-      </c>
-      <c r="I20" s="60">
-        <v>6</v>
-      </c>
-      <c r="J20" s="61">
-        <v>45</v>
-      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>130</v>
-      </c>
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
-      <c r="F21" s="60">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="G21" s="60">
-        <v>14</v>
-      </c>
-      <c r="H21" s="60">
-        <v>15</v>
-      </c>
-      <c r="I21" s="60">
-        <v>5</v>
-      </c>
-      <c r="J21" s="61">
-        <v>21</v>
-      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>131</v>
-      </c>
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
-      <c r="F22" s="60">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="G22" s="60">
-        <v>11</v>
-      </c>
-      <c r="H22" s="60">
-        <v>19</v>
-      </c>
-      <c r="I22" s="60">
-        <v>4</v>
-      </c>
-      <c r="J22" s="61">
-        <v>33</v>
-      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="61"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>132</v>
-      </c>
+      <c r="A23" s="46"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="F23" s="62">
-        <v>28.7</v>
-      </c>
-      <c r="G23" s="62">
-        <v>8</v>
-      </c>
-      <c r="H23" s="62">
-        <v>7</v>
-      </c>
-      <c r="I23" s="62">
-        <v>3</v>
-      </c>
-      <c r="J23" s="63">
-        <v>14</v>
-      </c>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="17"/>
@@ -5360,34 +5048,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="C1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="F1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="I1" s="68" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="J1" s="67" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5568,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>65</v>
@@ -5580,13 +5268,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
         <v>66</v>
@@ -5596,25 +5284,14 @@
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="29">
-        <v>55</v>
-      </c>
+      <c r="B14" s="29"/>
       <c r="C14" s="29"/>
       <c r="D14" s="29"/>
-      <c r="E14" s="29">
-        <v>1600</v>
-      </c>
-      <c r="F14" s="29">
-        <v>20</v>
-      </c>
-      <c r="G14" s="29">
-        <v>20</v>
-      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="29"/>
-      <c r="I14" s="30">
-        <f>SUM(B14:H14)</f>
-        <v>1695</v>
-      </c>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
@@ -5701,150 +5378,80 @@
         <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>44</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>136</v>
-      </c>
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
       <c r="E19" s="37"/>
-      <c r="F19" s="58">
-        <v>6</v>
-      </c>
-      <c r="G19" s="58">
-        <v>7</v>
-      </c>
-      <c r="H19" s="58">
-        <v>42</v>
-      </c>
-      <c r="I19" s="58">
-        <v>310</v>
-      </c>
-      <c r="J19" s="59">
-        <v>18</v>
-      </c>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>137</v>
-      </c>
+      <c r="A20" s="41"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
-      <c r="F20" s="60">
-        <v>5</v>
-      </c>
-      <c r="G20" s="60">
-        <v>2</v>
-      </c>
-      <c r="H20" s="60">
-        <v>11</v>
-      </c>
-      <c r="I20" s="60">
-        <v>95</v>
-      </c>
-      <c r="J20" s="61">
-        <v>6</v>
-      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>138</v>
-      </c>
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
-      <c r="F21" s="60">
-        <v>4</v>
-      </c>
-      <c r="G21" s="60">
-        <v>0</v>
-      </c>
-      <c r="H21" s="60">
-        <v>3</v>
-      </c>
-      <c r="I21" s="60">
-        <v>21</v>
-      </c>
-      <c r="J21" s="61">
-        <v>2</v>
-      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>139</v>
-      </c>
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
-      <c r="F22" s="60">
-        <v>5</v>
-      </c>
-      <c r="G22" s="60">
-        <v>1</v>
-      </c>
-      <c r="H22" s="60">
-        <v>8</v>
-      </c>
-      <c r="I22" s="60">
-        <v>64</v>
-      </c>
-      <c r="J22" s="61">
-        <v>4</v>
-      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="61"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>140</v>
-      </c>
+      <c r="A23" s="46"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="F23" s="62">
-        <v>4</v>
-      </c>
-      <c r="G23" s="62">
-        <v>0</v>
-      </c>
-      <c r="H23" s="62">
-        <v>2</v>
-      </c>
-      <c r="I23" s="62">
-        <v>12</v>
-      </c>
-      <c r="J23" s="63">
-        <v>1</v>
-      </c>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="17"/>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -2761,20 +2761,24 @@
         <v>336</v>
       </c>
       <c r="C14" s="29">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D14" s="29">
         <v>13440</v>
       </c>
       <c r="E14" s="29">
-        <v>5732</v>
-      </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
+        <v>10742</v>
+      </c>
+      <c r="F14" s="29">
+        <v>1200</v>
+      </c>
+      <c r="G14" s="29">
+        <v>625</v>
+      </c>
       <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>19708</v>
+        <v>26443</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="128">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -467,6 +467,49 @@
   </si>
   <si>
     <t>자원봉사자키트</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누적</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>(mm)</t>
+    </r>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -2863,7 +2906,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>30</v>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="129">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -509,6 +509,34 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>(mm)</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강수량</t>
     </r>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -1568,7 +1596,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>36</v>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -3343,9 +3343,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46269</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -3358,9 +3356,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46271</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3373,9 +3369,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46271</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -3962,9 +3956,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46099</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -3977,9 +3969,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46103</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3992,9 +3982,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46103</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -4581,9 +4569,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46038</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -4596,9 +4582,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46040</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -4611,9 +4595,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46040</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -5200,9 +5182,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46153</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -5215,9 +5195,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46153</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -5230,9 +5208,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46154</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★ 경영평가총괄TF팀\12. AX\재해지도 만들기_규식\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\Documents\Amaranth10\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="127">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -467,77 +467,6 @@
   </si>
   <si>
     <t>자원봉사자키트</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>강수량</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>(mm)</t>
-    </r>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>강수량</t>
-    </r>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1596,7 +1525,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>36</v>
@@ -2835,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="29">
-        <v>13440</v>
+        <v>35840</v>
       </c>
       <c r="E14" s="29">
         <v>10742</v>
@@ -2849,7 +2778,7 @@
       <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>26443</v>
+        <v>48843</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2934,7 +2863,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>30</v>
@@ -3343,7 +3272,9 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="22">
+        <v>46269</v>
+      </c>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -3356,7 +3287,9 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22"/>
+      <c r="B6" s="22">
+        <v>46271</v>
+      </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3369,7 +3302,9 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="22">
+        <v>46271</v>
+      </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -3956,7 +3891,9 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="22">
+        <v>46099</v>
+      </c>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -3969,7 +3906,9 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22"/>
+      <c r="B6" s="22">
+        <v>46103</v>
+      </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3982,7 +3921,9 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="22">
+        <v>46103</v>
+      </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -4569,7 +4510,9 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="22">
+        <v>46038</v>
+      </c>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -4582,7 +4525,9 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22"/>
+      <c r="B6" s="22">
+        <v>46040</v>
+      </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -4595,7 +4540,9 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="22">
+        <v>46040</v>
+      </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -5182,7 +5129,9 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="22">
+        <v>46153</v>
+      </c>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -5195,7 +5144,9 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22"/>
+      <c r="B6" s="22">
+        <v>46153</v>
+      </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -5208,7 +5159,9 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="22">
+        <v>46154</v>
+      </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\Documents\Amaranth10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★ 경영평가총괄TF팀\12. AX\재해지도 만들기_규식\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="129">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -467,6 +467,77 @@
   </si>
   <si>
     <t>자원봉사자키트</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누적</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>(mm)</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강수량</t>
+    </r>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1525,7 +1596,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>36</v>
@@ -2764,7 +2835,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="29">
-        <v>35840</v>
+        <v>13440</v>
       </c>
       <c r="E14" s="29">
         <v>10742</v>
@@ -2778,7 +2849,7 @@
       <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>48843</v>
+        <v>26443</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2863,7 +2934,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>30</v>
@@ -3272,9 +3343,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46269</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -3287,9 +3356,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46271</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3302,9 +3369,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46271</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -3891,9 +3956,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46099</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -3906,9 +3969,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46103</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3921,9 +3982,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46103</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -4510,9 +4569,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46038</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -4525,9 +4582,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46040</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -4540,9 +4595,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46040</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -5129,9 +5182,7 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="22">
-        <v>46153</v>
-      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="17"/>
       <c r="D5" s="78"/>
       <c r="E5" s="79"/>
@@ -5144,9 +5195,7 @@
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="22">
-        <v>46153</v>
-      </c>
+      <c r="B6" s="22"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -5159,9 +5208,7 @@
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22">
-        <v>46154</v>
-      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>

--- a/data/disaster_map_data.xlsx
+++ b/data/disaster_map_data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★ 경영평가총괄TF팀\12. AX\재해지도 만들기_규식\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="8280" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -1983,16 +1983,28 @@
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
+      <c r="B14" s="29">
+        <v>336</v>
+      </c>
+      <c r="C14" s="29">
+        <v>100</v>
+      </c>
+      <c r="D14" s="29">
+        <v>35840</v>
+      </c>
+      <c r="E14" s="29">
+        <v>10742</v>
+      </c>
+      <c r="F14" s="29">
+        <v>1200</v>
+      </c>
+      <c r="G14" s="29">
+        <v>625</v>
+      </c>
       <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>0</v>
+        <v>48843</v>
       </c>
     </row>
     <row r="15" spans="1:9">
